--- a/графики/График_платежей_Останкино_22_10_26.xlsx
+++ b/графики/График_платежей_Останкино_22_10_26.xlsx
@@ -1,31 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Uaer4\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9739CB7F-0184-4876-A21B-CE75FE4059A7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9304F98B-9671-4904-84CA-98B60A051026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="График платежей" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>

--- a/графики/График_платежей_Останкино_22_10_26.xlsx
+++ b/графики/График_платежей_Останкино_22_10_26.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9304F98B-9671-4904-84CA-98B60A051026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D162326-C95D-4A87-8F5E-B8887C949400}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="График платежей" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -739,7 +745,7 @@
   <dimension ref="A1:R31"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.85546875" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
     <col min="2" max="3" width="15" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="4" max="4" width="15" customWidth="1" collapsed="1"/>
     <col min="5" max="17" width="15" customWidth="1"/>
@@ -1367,7 +1373,10 @@
       </c>
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
-      <c r="R23" s="20"/>
+      <c r="R23" s="20">
+        <f>SUM(D23:Q23)</f>
+        <v>20628000</v>
+      </c>
     </row>
     <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="34" t="s">
@@ -1449,7 +1458,10 @@
       <c r="O27" s="5"/>
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
-      <c r="R27" s="20"/>
+      <c r="R27" s="20">
+        <f>SUM(D27:Q27)</f>
+        <v>10464000</v>
+      </c>
     </row>
     <row r="28" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="34" t="s">
